--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260617.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260617.xlsx
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,240,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>1,240,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>7,550,000</t>
+          <t>1,080,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,080,000</t>
+          <t>7,550,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,560,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>1,560,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
